--- a/notebook/sample_excel/INSURANCE_PDF_STUFF.xlsx
+++ b/notebook/sample_excel/INSURANCE_PDF_STUFF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaustubh.keny\Projects\OFFICE PROJECTS\rep_fsparse\notebook\sample_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F50A812-78BB-4D37-A5D8-7535E90B05BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC96A38-8EDE-4A7A-B219-1A7919969C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questionare" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3945" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3954" uniqueCount="878">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -2670,6 +2670,9 @@
   </si>
   <si>
     <t>GF config</t>
+  </si>
+  <si>
+    <t>Nil</t>
   </si>
 </sst>
 </file>
@@ -2707,7 +2710,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2738,6 +2741,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2766,7 +2781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2781,6 +2796,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27666,11 +27684,11 @@
         <v>875</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
         <v>79</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="15" t="s">
         <v>361</v>
       </c>
     </row>
@@ -27681,6 +27699,9 @@
       <c r="B9" s="11" t="s">
         <v>398</v>
       </c>
+      <c r="G9" s="13" t="s">
+        <v>875</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
@@ -27703,6 +27724,12 @@
       <c r="B11" s="11" t="s">
         <v>447</v>
       </c>
+      <c r="G11" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>875</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -27711,6 +27738,9 @@
       <c r="B12" s="12" t="s">
         <v>872</v>
       </c>
+      <c r="G12" s="13" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -27719,6 +27749,12 @@
       <c r="B13" s="11" t="s">
         <v>480</v>
       </c>
+      <c r="G13" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>875</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -27744,7 +27780,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>88</v>
       </c>
@@ -27752,7 +27788,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>89</v>
       </c>
@@ -27760,7 +27796,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>90</v>
       </c>
@@ -27768,7 +27804,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>91</v>
       </c>
@@ -27776,7 +27812,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>92</v>
       </c>
@@ -27784,28 +27820,37 @@
         <v>712</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>93</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G22" s="13" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>94</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G23" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>112</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>873</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>877</v>
       </c>
     </row>
   </sheetData>

--- a/notebook/sample_excel/INSURANCE_PDF_STUFF.xlsx
+++ b/notebook/sample_excel/INSURANCE_PDF_STUFF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaustubh.keny\Projects\OFFICE PROJECTS\rep_fsparse\notebook\sample_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC96A38-8EDE-4A7A-B219-1A7919969C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9E16C4-6F79-4CA1-899C-E7F59300CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3954" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="878">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -27780,7 +27780,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>88</v>
       </c>
@@ -27788,7 +27788,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>89</v>
       </c>
@@ -27796,15 +27796,21 @@
         <v>668</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>90</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>91</v>
       </c>
@@ -27812,7 +27818,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>92</v>
       </c>
@@ -27820,7 +27826,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>93</v>
       </c>
@@ -27831,7 +27837,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>94</v>
       </c>
@@ -27842,7 +27848,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>112</v>
       </c>
